--- a/src/Excelsior.Tests/FieldSupportTests.Builder_Column_AcceptsFieldExpression.verified.xlsx
+++ b/src/Excelsior.Tests/FieldSupportTests.Builder_Column_AcceptsFieldExpression.verified.xlsx
@@ -51,7 +51,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
